--- a/ibmi_reservations.xlsx
+++ b/ibmi_reservations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\bob-for-ibmi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98927687-EBA0-4B0E-B887-FFE677BB3720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0D21948F-C8A6-4FEB-AC7B-5352BD6E1255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{997857C9-1777-4110-8BDE-E8E21DDACA3C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A3F0483B-9B68-49F7-8F81-A67C573FB50D}"/>
   </bookViews>
   <sheets>
     <sheet name="ibmi_reservations" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="191">
   <si>
     <t>Name</t>
   </si>
@@ -61,109 +61,538 @@
     <t>Shared With</t>
   </si>
   <si>
-    <t>IBM i 7.6 IBM Cloud PowerVS VSI - 2026-08-21 - Created by AskTZ</t>
+    <t>IBM i 7.6 IBM Cloud PowerVS VSI - 2026-09-01 - Created by AskTZ</t>
   </si>
   <si>
     <t>Ready</t>
   </si>
   <si>
-    <t>itzpvs-ucc9hi0k</t>
-  </si>
-  <si>
-    <t>161.156.22.60</t>
+    <t>itzpvs-p96pne1k</t>
   </si>
   <si>
     <t>ITZUSER</t>
   </si>
   <si>
-    <t>7-vw_gC0OT(FKit</t>
-  </si>
-  <si>
-    <t>https://techzone.ibm.com/my/requests/6a8877f865158f1b16546f28</t>
-  </si>
-  <si>
-    <t>2026-08-21 16:10:00Z-2026-08-28 16:10:00 UTC</t>
+    <t>4-CpraZu_Cd47i)</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a96e891e0d536c4ab67607f</t>
+  </si>
+  <si>
+    <t>2026-09-01 15:40:00 UTC-2026-09-08 15:40:00 UTC</t>
   </si>
   <si>
     <t>eu-de</t>
   </si>
   <si>
-    <t>6a8877f865158f1b16546f28</t>
-  </si>
-  <si>
-    <t>bart_bogaerts@yahoo.com</t>
-  </si>
-  <si>
-    <t>IBM i 7.6 IBM Cloud PowerVS VSI - 2026-08-17 - Created by AskTZ</t>
-  </si>
-  <si>
-    <t>itzpvs-mj11hc0k</t>
-  </si>
-  <si>
-    <t>ryK==G13E2O%3o_</t>
-  </si>
-  <si>
-    <t>https://techzone.ibm.com/my/requests/6a856478b4e22cae9cf3d058</t>
-  </si>
-  <si>
-    <t>2026-08-17 14:51:00Z-2026-08-24 14:51:00 UTC</t>
-  </si>
-  <si>
-    <t>6a856478b4e22cae9cf3d058</t>
-  </si>
-  <si>
-    <t>itzpvs-bl11hc0k</t>
-  </si>
-  <si>
-    <t>vS43dgO@p=Mj5i-</t>
-  </si>
-  <si>
-    <t>https://techzone.ibm.com/my/requests/6a8564788e3f5d1d782f28ac</t>
-  </si>
-  <si>
-    <t>2026-08-17 14:50:00Z-2026-08-24 14:50:00 UTC</t>
-  </si>
-  <si>
-    <t>6a8564788e3f5d1d782f28ac</t>
-  </si>
-  <si>
-    <t>itzpvs-acdq280k</t>
-  </si>
-  <si>
-    <t>161.156.191.98</t>
-  </si>
-  <si>
-    <t>2*VI7%5b*Gdob1V</t>
-  </si>
-  <si>
-    <t>https://techzone.ibm.com/my/requests/6a831dfe55cacf5a51962fd4</t>
-  </si>
-  <si>
-    <t>2026-08-17 14:44:00Z-2026-09-07 14:45:00 UTC</t>
-  </si>
-  <si>
-    <t>6a831dfe55cacf5a51962fd4</t>
-  </si>
-  <si>
-    <t>bart_bogaerts@be.ibm.com;steve.lievens@be.ibm.com</t>
-  </si>
-  <si>
-    <t>itzpvs-ombq280k</t>
-  </si>
-  <si>
-    <t>161.156.22.197</t>
-  </si>
-  <si>
-    <t>)l(Uk7Tw+6QTz6)</t>
-  </si>
-  <si>
-    <t>https://techzone.ibm.com/my/requests/6a831dfb0fbc87ac8b402182</t>
-  </si>
-  <si>
-    <t>2026-08-17 14:43:00Z-2026-09-07 14:45:00 UTC</t>
-  </si>
-  <si>
-    <t>6a831dfb0fbc87ac8b402182</t>
+    <t>6a96e891e0d536c4ab67607f</t>
+  </si>
+  <si>
+    <t>jan.wallays@europabank.be</t>
+  </si>
+  <si>
+    <t>itzpvs-iov7ce1k</t>
+  </si>
+  <si>
+    <t>ro.tCGCI%17gp-4</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a96b950475f4a72c6581274</t>
+  </si>
+  <si>
+    <t>2026-09-01 12:20:00 UTC-2026-09-08 12:20:00 UTC</t>
+  </si>
+  <si>
+    <t>6a96b950475f4a72c6581274</t>
+  </si>
+  <si>
+    <t>julien@afinit.be</t>
+  </si>
+  <si>
+    <t>itzpvs-iav7ce1k</t>
+  </si>
+  <si>
+    <t>7%0k3(nS5HUoYfb</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a96b95037a7d2188e329aa0</t>
+  </si>
+  <si>
+    <t>6a96b95037a7d2188e329aa0</t>
+  </si>
+  <si>
+    <t>koen.loffeld@alpinedigital.be;ludovic.gasc@be.ibm.com</t>
+  </si>
+  <si>
+    <t>itzpvs-f75u6e1k</t>
+  </si>
+  <si>
+    <t>82a=)Sk_pVuiR6c</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a96a3935ffc726f6e479942</t>
+  </si>
+  <si>
+    <t>2026-09-01 10:35:00 UTC-2026-09-08 10:35:00 UTC</t>
+  </si>
+  <si>
+    <t>6a96a3935ffc726f6e479942</t>
+  </si>
+  <si>
+    <t>pascale.crosiers@ascoindustries.com</t>
+  </si>
+  <si>
+    <t>itzpvs-fm5u6e1k</t>
+  </si>
+  <si>
+    <t>IX+=rVt=98umv35</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a96a3921ff526a9a16bd42f</t>
+  </si>
+  <si>
+    <t>6a96a3921ff526a9a16bd42f</t>
+  </si>
+  <si>
+    <t>wannesmachiels@gmail.com</t>
+  </si>
+  <si>
+    <t>itzpvs-cvdd1e1k</t>
+  </si>
+  <si>
+    <t>161.156.181.22</t>
+  </si>
+  <si>
+    <t>bSE1*hl)*7vhOtO</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a968cf02ce49c741529063d</t>
+  </si>
+  <si>
+    <t>2026-09-01 09:15:00 UTC-2026-09-08 09:15:00 UTC</t>
+  </si>
+  <si>
+    <t>6a968cf02ce49c741529063d</t>
+  </si>
+  <si>
+    <t>sabine.dejonghe@axians.com</t>
+  </si>
+  <si>
+    <t>itzpvs-bccd1e1k</t>
+  </si>
+  <si>
+    <t>161.156.139.26</t>
+  </si>
+  <si>
+    <t>kIz4(-pfi0BXG5N</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a968cef2ce49c741529063c</t>
+  </si>
+  <si>
+    <t>2026-09-01 09:20:00 UTC-2026-09-08 09:20:00 UTC</t>
+  </si>
+  <si>
+    <t>6a968cef2ce49c741529063c</t>
+  </si>
+  <si>
+    <t>veerle.kerckvoorde@axians.com</t>
+  </si>
+  <si>
+    <t>itzpvs-cecd1e1k</t>
+  </si>
+  <si>
+    <t>161.156.22.70</t>
+  </si>
+  <si>
+    <t>9Ue0@)1HxVACWhV</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a968cef3f4ea1d69c46179a</t>
+  </si>
+  <si>
+    <t>2026-09-02 01:00:00 UTC-2026-09-09 01:00:00 UTC</t>
+  </si>
+  <si>
+    <t>6a968cef3f4ea1d69c46179a</t>
+  </si>
+  <si>
+    <t>ludovic.gasc@be.ibm.com</t>
+  </si>
+  <si>
+    <t>itzpvs-oh7d1e1k</t>
+  </si>
+  <si>
+    <t>+7.wlYIt-q7EK30</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a968cef8b53211ac4e23789</t>
+  </si>
+  <si>
+    <t>6a968cef8b53211ac4e23789</t>
+  </si>
+  <si>
+    <t>ann.desmet@axians.com</t>
+  </si>
+  <si>
+    <t>itzpvs-0nad1e1k</t>
+  </si>
+  <si>
+    <t>161.156.22.98</t>
+  </si>
+  <si>
+    <t>Nn=%3W3oen+r9yp</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a968cef016286aae1d24818</t>
+  </si>
+  <si>
+    <t>6a968cef016286aae1d24818</t>
+  </si>
+  <si>
+    <t>willy@business-systems.be</t>
+  </si>
+  <si>
+    <t>itzpvs-39bd1e1k</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a968cef6e2cf054c10a1a72</t>
+  </si>
+  <si>
+    <t>6a968cef6e2cf054c10a1a72</t>
+  </si>
+  <si>
+    <t>paul.nicolay@cegeka.com</t>
+  </si>
+  <si>
+    <t>itzpvs-n0bd1e1k</t>
+  </si>
+  <si>
+    <t>161.156.139.12</t>
+  </si>
+  <si>
+    <t>5.t5MQ=%2NB2mqX</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a968ceeaad1a0106590de69</t>
+  </si>
+  <si>
+    <t>6a968ceeaad1a0106590de69</t>
+  </si>
+  <si>
+    <t>steven.vanbosch@colruytgroup.com</t>
+  </si>
+  <si>
+    <t>itzpvs-6hortd1k</t>
+  </si>
+  <si>
+    <t>9_FVse4(LVML%FF</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a967e6a3a5b84596ead2b2f</t>
+  </si>
+  <si>
+    <t>2026-09-01 08:15:00 UTC-2026-09-08 08:15:00 UTC</t>
+  </si>
+  <si>
+    <t>6a967e6a3a5b84596ead2b2f</t>
+  </si>
+  <si>
+    <t>joris.coppejans@europabank.be</t>
+  </si>
+  <si>
+    <t>itzpvs-rksrtd1k</t>
+  </si>
+  <si>
+    <t>*lBEsI=c+b30i7P</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a967e69c6590aee26c108ba</t>
+  </si>
+  <si>
+    <t>6a967e69c6590aee26c108ba</t>
+  </si>
+  <si>
+    <t>IBM i 7.6 IBM Cloud PowerVS VSI - 2026-08-31 - Created by AskTZ</t>
+  </si>
+  <si>
+    <t>itzpvs-hjal3c1k</t>
+  </si>
+  <si>
+    <t>161.156.153.35</t>
+  </si>
+  <si>
+    <t>q12ZdP.L8-z4pSr</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a959004849007ddb330994f</t>
+  </si>
+  <si>
+    <t>2026-08-31 15:05:00 UTC-2026-09-07 15:05:00 UTC</t>
+  </si>
+  <si>
+    <t>6a959004849007ddb330994f</t>
+  </si>
+  <si>
+    <t>david.vanmanshoven@axians.com</t>
+  </si>
+  <si>
+    <t>itzpvs-j8cl3c1k</t>
+  </si>
+  <si>
+    <t>161.156.191.59</t>
+  </si>
+  <si>
+    <t>4l.e+2NE6e(rgs6</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a9590023a5b84596ead2a0a</t>
+  </si>
+  <si>
+    <t>6a9590023a5b84596ead2a0a</t>
+  </si>
+  <si>
+    <t>marie.gris@heliaq.fr</t>
+  </si>
+  <si>
+    <t>itzpvs-lt9l3c1k</t>
+  </si>
+  <si>
+    <t>161.156.22.27</t>
+  </si>
+  <si>
+    <t>BMPD01_(xrY6B0b</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a9590012215089a9cb62d66</t>
+  </si>
+  <si>
+    <t>6a9590012215089a9cb62d66</t>
+  </si>
+  <si>
+    <t>julien_vandenberg@eupen.com</t>
+  </si>
+  <si>
+    <t>itzpvs-fn9l3c1k</t>
+  </si>
+  <si>
+    <t>161.156.22.11</t>
+  </si>
+  <si>
+    <t>dvco@7*Y2bvG0Rj</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a959001475f4a72c6581140</t>
+  </si>
+  <si>
+    <t>6a959001475f4a72c6581140</t>
+  </si>
+  <si>
+    <t>yves_delannay@eupen.com</t>
+  </si>
+  <si>
+    <t>itzpvs-t0bl3c1k</t>
+  </si>
+  <si>
+    <t>=)o488gDTLS=pDC</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a9590019f66eb57ed5fae50</t>
+  </si>
+  <si>
+    <t>6a9590019f66eb57ed5fae50</t>
+  </si>
+  <si>
+    <t>brent@marcit.be</t>
+  </si>
+  <si>
+    <t>itzpvs-187l3c1k</t>
+  </si>
+  <si>
+    <t>w5wDM7Xbd*_5W.N</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a959001631388e000fe0b3a</t>
+  </si>
+  <si>
+    <t>6a959001631388e000fe0b3a</t>
+  </si>
+  <si>
+    <t>mariuslr@mlr-consulting.com</t>
+  </si>
+  <si>
+    <t>itzpvs-0l6l3c1k</t>
+  </si>
+  <si>
+    <t>161.156.191.74</t>
+  </si>
+  <si>
+    <t>8OY(IP86.cqlkhM</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a959001016286aae1d245c0</t>
+  </si>
+  <si>
+    <t>6a959001016286aae1d245c0</t>
+  </si>
+  <si>
+    <t>jim.bourgoignie@mp-i.eu</t>
+  </si>
+  <si>
+    <t>itzpvs-1u8l3c1k</t>
+  </si>
+  <si>
+    <t>161.156.22.252</t>
+  </si>
+  <si>
+    <t>x5RilMVA%C1JK4(</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a959001198f09546b278e2a</t>
+  </si>
+  <si>
+    <t>6a959001198f09546b278e2a</t>
+  </si>
+  <si>
+    <t>sabienasj@gmail.com</t>
+  </si>
+  <si>
+    <t>itzpvs-9c8l3c1k</t>
+  </si>
+  <si>
+    <t>161.156.22.46</t>
+  </si>
+  <si>
+    <t>qag0@jV-3W7Z)_+</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a9590012041e1b0af89c565</t>
+  </si>
+  <si>
+    <t>6a9590012041e1b0af89c565</t>
+  </si>
+  <si>
+    <t>p.jimenezmogollon@gmail.com</t>
+  </si>
+  <si>
+    <t>itzpvs-477l3c1k</t>
+  </si>
+  <si>
+    <t>@OCTmrZ+83n*dQ+</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a9590008eaf77fb0afcb28f</t>
+  </si>
+  <si>
+    <t>6a9590008eaf77fb0afcb28f</t>
+  </si>
+  <si>
+    <t>bart.vandeputte@tdsynnex.com</t>
+  </si>
+  <si>
+    <t>itzpvs-nk1bsb1k</t>
+  </si>
+  <si>
+    <t>161.156.153.6</t>
+  </si>
+  <si>
+    <t>7*n8N8t%GbW6+zT</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a957206631388e000fe0b01</t>
+  </si>
+  <si>
+    <t>2026-08-31 12:55:00 UTC-2026-09-07 12:55:00 UTC</t>
+  </si>
+  <si>
+    <t>6a957206631388e000fe0b01</t>
+  </si>
+  <si>
+    <t>thomas.nauwelaerts@vandeput.be</t>
+  </si>
+  <si>
+    <t>itzpvs-r00bsb1k</t>
+  </si>
+  <si>
+    <t>8weCMmz6s@S=1l2</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a957206475f4a72c6581108</t>
+  </si>
+  <si>
+    <t>6a957206475f4a72c6581108</t>
+  </si>
+  <si>
+    <t>michel.debondt@vandeput.be</t>
+  </si>
+  <si>
+    <t>itzpvs-e05bsb1k</t>
+  </si>
+  <si>
+    <t>161.156.139.50</t>
+  </si>
+  <si>
+    <t>b4*Ac*7RlII%YUB</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a95720679199abda8266171</t>
+  </si>
+  <si>
+    <t>6a95720679199abda8266171</t>
+  </si>
+  <si>
+    <t>benny.vanbelle@vandeput.be</t>
+  </si>
+  <si>
+    <t>itzpvs-0o2bsb1k</t>
+  </si>
+  <si>
+    <t>%V)z1m0Emyyt+U-</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a957206c6590aee26c1063a</t>
+  </si>
+  <si>
+    <t>6a957206c6590aee26c1063a</t>
+  </si>
+  <si>
+    <t>johan.dingenen@vandeput.be</t>
+  </si>
+  <si>
+    <t>itzpvs-navasb1k</t>
+  </si>
+  <si>
+    <t>161.156.191.2</t>
+  </si>
+  <si>
+    <t>9+Lfh3h+FSZ+rHZ</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a9572055aa00a7e843ca1d1</t>
+  </si>
+  <si>
+    <t>6a9572055aa00a7e843ca1d1</t>
+  </si>
+  <si>
+    <t>toshaan@vantosh.com</t>
+  </si>
+  <si>
+    <t>itzpvs-lfvasb1k</t>
+  </si>
+  <si>
+    <t>161.156.147.51</t>
+  </si>
+  <si>
+    <t>v+x2C2mzjtP(hLF</t>
+  </si>
+  <si>
+    <t>https://techzone.ibm.com/my/requests/6a957205a5e90a7a31c975c4</t>
+  </si>
+  <si>
+    <t>6a957205a5e90a7a31c975c4</t>
+  </si>
+  <si>
+    <t>marc@marcit.be</t>
   </si>
 </sst>
 </file>
@@ -1035,23 +1464,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1DE7D1-69CD-438B-BEDD-D2B91D897670}">
-  <dimension ref="A1:M6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C7EDAAC-864E-4FD7-96A9-1B0997A0D8FB}">
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="60.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="58.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1108,199 +1537,1228 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
+      <c r="E2" s="1">
+        <v>161156181115</v>
       </c>
       <c r="F2">
         <v>22</v>
       </c>
       <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
       <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1">
+        <v>161156136115</v>
+      </c>
+      <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1">
-        <v>161156136125</v>
-      </c>
-      <c r="F3">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1">
+        <v>161156154165</v>
+      </c>
+      <c r="F4">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="1">
-        <v>161156136130</v>
-      </c>
-      <c r="F4">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
         <v>32</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>33</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1">
+        <v>161156147211</v>
+      </c>
+      <c r="F5">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>36</v>
       </c>
-      <c r="F5">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" t="s">
         <v>38</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>39</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1">
+        <v>161156181156</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
         <v>42</v>
       </c>
-      <c r="E6" t="s">
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" t="s">
         <v>43</v>
       </c>
-      <c r="F6">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="M6" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
         <v>45</v>
       </c>
-      <c r="J6" t="s">
+      <c r="E7" t="s">
         <v>46</v>
       </c>
-      <c r="K6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
         <v>47</v>
       </c>
-      <c r="M6" t="s">
-        <v>23</v>
+      <c r="I7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="1">
+        <v>161156147251</v>
+      </c>
+      <c r="F10">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11">
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="1">
+        <v>161156154246</v>
+      </c>
+      <c r="F12">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="e">
+        <f>+yq1El-YfdS381Y</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13">
+        <v>22</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" t="s">
+        <v>85</v>
+      </c>
+      <c r="M13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="1">
+        <v>161156191166</v>
+      </c>
+      <c r="F14">
+        <v>22</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" t="s">
+        <v>91</v>
+      </c>
+      <c r="M14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="1">
+        <v>161156191108</v>
+      </c>
+      <c r="F15">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" t="s">
+        <v>96</v>
+      </c>
+      <c r="M15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" t="s">
+        <v>103</v>
+      </c>
+      <c r="M16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17" t="s">
+        <v>109</v>
+      </c>
+      <c r="M17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18" t="s">
+        <v>115</v>
+      </c>
+      <c r="M18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19">
+        <v>22</v>
+      </c>
+      <c r="G19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" t="s">
+        <v>102</v>
+      </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19" t="s">
+        <v>121</v>
+      </c>
+      <c r="M19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="1">
+        <v>161156136134</v>
+      </c>
+      <c r="F20">
+        <v>22</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" t="s">
+        <v>125</v>
+      </c>
+      <c r="J20" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" t="s">
+        <v>126</v>
+      </c>
+      <c r="M20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="1">
+        <v>161156154118</v>
+      </c>
+      <c r="F21">
+        <v>22</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" t="s">
+        <v>131</v>
+      </c>
+      <c r="M21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s">
+        <v>135</v>
+      </c>
+      <c r="I22" t="s">
+        <v>136</v>
+      </c>
+      <c r="J22" t="s">
+        <v>102</v>
+      </c>
+      <c r="K22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22" t="s">
+        <v>137</v>
+      </c>
+      <c r="M22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23">
+        <v>22</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23" t="s">
+        <v>143</v>
+      </c>
+      <c r="M23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24">
+        <v>22</v>
+      </c>
+      <c r="G24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" t="s">
+        <v>148</v>
+      </c>
+      <c r="J24" t="s">
+        <v>102</v>
+      </c>
+      <c r="K24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" t="s">
+        <v>149</v>
+      </c>
+      <c r="M24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" s="1">
+        <v>161156139116</v>
+      </c>
+      <c r="F25">
+        <v>22</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" t="s">
+        <v>154</v>
+      </c>
+      <c r="M25" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26">
+        <v>22</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>158</v>
+      </c>
+      <c r="I26" t="s">
+        <v>159</v>
+      </c>
+      <c r="J26" t="s">
+        <v>160</v>
+      </c>
+      <c r="K26" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" t="s">
+        <v>161</v>
+      </c>
+      <c r="M26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s">
+        <v>163</v>
+      </c>
+      <c r="E27" s="1">
+        <v>161156136162</v>
+      </c>
+      <c r="F27">
+        <v>22</v>
+      </c>
+      <c r="G27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" t="s">
+        <v>164</v>
+      </c>
+      <c r="I27" t="s">
+        <v>165</v>
+      </c>
+      <c r="J27" t="s">
+        <v>160</v>
+      </c>
+      <c r="K27" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" t="s">
+        <v>166</v>
+      </c>
+      <c r="M27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28">
+        <v>22</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" t="s">
+        <v>171</v>
+      </c>
+      <c r="J28" t="s">
+        <v>160</v>
+      </c>
+      <c r="K28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" t="s">
+        <v>172</v>
+      </c>
+      <c r="M28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="1">
+        <v>161156153180</v>
+      </c>
+      <c r="F29">
+        <v>22</v>
+      </c>
+      <c r="G29" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" t="s">
+        <v>176</v>
+      </c>
+      <c r="J29" t="s">
+        <v>160</v>
+      </c>
+      <c r="K29" t="s">
+        <v>20</v>
+      </c>
+      <c r="L29" t="s">
+        <v>177</v>
+      </c>
+      <c r="M29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30">
+        <v>22</v>
+      </c>
+      <c r="G30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" t="s">
+        <v>181</v>
+      </c>
+      <c r="I30" t="s">
+        <v>182</v>
+      </c>
+      <c r="J30" t="s">
+        <v>160</v>
+      </c>
+      <c r="K30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" t="s">
+        <v>183</v>
+      </c>
+      <c r="M30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E31" t="s">
+        <v>186</v>
+      </c>
+      <c r="F31">
+        <v>22</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>187</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="J31" t="s">
+        <v>160</v>
+      </c>
+      <c r="K31" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" t="s">
+        <v>189</v>
+      </c>
+      <c r="M31" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{3242078F-961D-4826-969B-CFB111537FF8}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{A0F02FD9-F25C-4B94-9BFC-03A812E6EB64}"/>
-    <hyperlink ref="I4" r:id="rId3" xr:uid="{96EB7326-4EBA-4189-B08D-8F6C47A74586}"/>
-    <hyperlink ref="I5" r:id="rId4" xr:uid="{B0997F1F-A0F7-467A-A6C0-DE0479859196}"/>
-    <hyperlink ref="I6" r:id="rId5" xr:uid="{CE1D9ACB-5B66-4582-8290-6127FAF5D2A4}"/>
+    <hyperlink ref="I31" r:id="rId1" xr:uid="{3A14CCD2-7ACC-4F96-A993-6AEC5CDAF50B}"/>
+    <hyperlink ref="I15" r:id="rId2" xr:uid="{0E573DE1-6DED-4DE0-829C-4A80331DCCDA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
